--- a/product-definitions/spreadsheet/acoustic-backscatter-winds.xlsx
+++ b/product-definitions/spreadsheet/acoustic-backscatter-winds.xlsx
@@ -257,7 +257,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -287,11 +287,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -308,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -350,7 +345,7 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -365,7 +360,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
@@ -1934,7 +1928,7 @@
       </c>
       <c r="I20" s="17"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="10" t="s">
         <v>20</v>
       </c>
@@ -1943,7 +1937,7 @@
       </c>
       <c r="I21" s="17"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="10" t="s">
         <v>22</v>
       </c>
@@ -1951,7 +1945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="10" t="s">
         <v>30</v>
       </c>
@@ -1959,7 +1953,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="B24" s="10" t="s">
         <v>24</v>
       </c>
@@ -1967,16 +1961,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="C25" s="12"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="16"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="10" t="s">
         <v>11</v>
       </c>
@@ -1984,7 +1978,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="B28" s="10" t="s">
         <v>13</v>
       </c>
@@ -1992,7 +1986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="10" t="s">
         <v>2</v>
       </c>
@@ -2000,7 +1994,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="B30" s="10" t="s">
         <v>14</v>
       </c>
@@ -2008,7 +2002,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="10" t="s">
         <v>15</v>
       </c>
@@ -2016,7 +2010,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="B32" s="10" t="s">
         <v>17</v>
       </c>
@@ -2024,7 +2018,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="B33" s="10" t="s">
         <v>20</v>
       </c>
@@ -2032,7 +2026,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="B34" s="10" t="s">
         <v>22</v>
       </c>
@@ -2040,7 +2034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="10" t="s">
         <v>30</v>
       </c>
@@ -2048,7 +2042,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="B36" s="10" t="s">
         <v>24</v>
       </c>
@@ -2056,16 +2050,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="C37" s="16"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C38" s="16"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="B39" s="10" t="s">
         <v>11</v>
       </c>
@@ -2073,7 +2067,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="B40" s="10" t="s">
         <v>13</v>
       </c>
@@ -2081,7 +2075,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="B41" s="10" t="s">
         <v>2</v>
       </c>
@@ -2089,7 +2083,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="10" t="s">
         <v>14</v>
       </c>
@@ -2097,7 +2091,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="B43" s="10" t="s">
         <v>15</v>
       </c>
@@ -2105,7 +2099,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="B44" s="10" t="s">
         <v>17</v>
       </c>
@@ -2113,7 +2107,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="B45" s="10" t="s">
         <v>20</v>
       </c>
@@ -2121,7 +2115,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="B46" s="10" t="s">
         <v>22</v>
       </c>
@@ -2129,7 +2123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="B47" s="10" t="s">
         <v>30</v>
       </c>
@@ -2137,7 +2131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="B48" s="10" t="s">
         <v>24</v>
       </c>
@@ -2145,16 +2139,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="C49" s="16"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="10" t="s">
         <v>38</v>
       </c>
       <c r="C50" s="16"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="B51" s="10" t="s">
         <v>11</v>
       </c>
@@ -2162,7 +2156,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="B52" s="10" t="s">
         <v>13</v>
       </c>
@@ -2170,7 +2164,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="B53" s="10" t="s">
         <v>2</v>
       </c>
@@ -2178,7 +2172,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="B54" s="10" t="s">
         <v>14</v>
       </c>
@@ -2186,7 +2180,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="B55" s="10" t="s">
         <v>15</v>
       </c>
@@ -2194,7 +2188,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="B56" s="10" t="s">
         <v>17</v>
       </c>
@@ -2202,7 +2196,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="B57" s="10" t="s">
         <v>20</v>
       </c>
@@ -2210,7 +2204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="B58" s="10" t="s">
         <v>22</v>
       </c>
@@ -2218,7 +2212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="B59" s="10" t="s">
         <v>30</v>
       </c>
@@ -2226,7 +2220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="B60" s="10" t="s">
         <v>24</v>
       </c>
@@ -2234,16 +2228,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="C61" s="16"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="10" t="s">
         <v>40</v>
       </c>
       <c r="C62" s="16"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="B63" s="10" t="s">
         <v>11</v>
       </c>
@@ -2251,7 +2245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="B64" s="10" t="s">
         <v>13</v>
       </c>
@@ -2259,7 +2253,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="B65" s="10" t="s">
         <v>2</v>
       </c>
@@ -2267,7 +2261,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="B66" s="10" t="s">
         <v>14</v>
       </c>
@@ -2275,7 +2269,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="B67" s="10" t="s">
         <v>15</v>
       </c>
@@ -2283,7 +2277,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="B68" s="10" t="s">
         <v>17</v>
       </c>
@@ -2291,7 +2285,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="10" t="s">
         <v>20</v>
       </c>
@@ -2299,7 +2293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="B70" s="10" t="s">
         <v>22</v>
       </c>
@@ -2307,7 +2301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="B71" s="10" t="s">
         <v>30</v>
       </c>
@@ -2315,7 +2309,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="B72" s="10" t="s">
         <v>24</v>
       </c>
@@ -2323,16 +2317,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="C73" s="16"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C74" s="16"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="B75" s="10" t="s">
         <v>11</v>
       </c>
@@ -2340,7 +2334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="B76" s="10" t="s">
         <v>13</v>
       </c>
@@ -2348,7 +2342,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="B77" s="10" t="s">
         <v>2</v>
       </c>
@@ -2356,7 +2350,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="10" t="s">
         <v>14</v>
       </c>
@@ -2364,7 +2358,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="B79" s="10" t="s">
         <v>15</v>
       </c>
@@ -2372,7 +2366,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="B80" s="10" t="s">
         <v>17</v>
       </c>
@@ -2380,7 +2374,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="B81" s="10" t="s">
         <v>20</v>
       </c>
@@ -2388,7 +2382,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="B82" s="10" t="s">
         <v>22</v>
       </c>
@@ -2396,7 +2390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="B83" s="10" t="s">
         <v>30</v>
       </c>
@@ -2404,7 +2398,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="B84" s="10" t="s">
         <v>24</v>
       </c>
@@ -2412,16 +2406,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="C85" s="16"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="10" t="s">
         <v>44</v>
       </c>
       <c r="C86" s="16"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="B87" s="10" t="s">
         <v>11</v>
       </c>
@@ -2429,7 +2423,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="B88" s="10" t="s">
         <v>13</v>
       </c>
@@ -2437,7 +2431,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="B89" s="10" t="s">
         <v>2</v>
       </c>
@@ -2445,7 +2439,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="B90" s="10" t="s">
         <v>14</v>
       </c>
@@ -2454,7 +2448,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="B91" s="10" t="s">
         <v>15</v>
       </c>
@@ -2462,7 +2456,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="B92" s="10" t="s">
         <v>17</v>
       </c>
@@ -2470,7 +2464,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="B93" s="10" t="s">
         <v>20</v>
       </c>
@@ -2478,7 +2472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="B94" s="10" t="s">
         <v>22</v>
       </c>
@@ -2486,7 +2480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="B95" s="10" t="s">
         <v>30</v>
       </c>
@@ -2494,7 +2488,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="B96" s="10" t="s">
         <v>24</v>
       </c>
@@ -2502,16 +2496,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="C97" s="16"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="10" t="s">
         <v>47</v>
       </c>
       <c r="C98" s="16"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="10" t="s">
         <v>11</v>
       </c>
@@ -2519,7 +2513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="B100" s="10" t="s">
         <v>13</v>
       </c>
@@ -2527,7 +2521,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="B101" s="10" t="s">
         <v>2</v>
       </c>
@@ -2535,7 +2529,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="B102" s="10" t="s">
         <v>14</v>
       </c>
@@ -2544,7 +2538,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="B103" s="10" t="s">
         <v>15</v>
       </c>
@@ -2552,7 +2546,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="B104" s="10" t="s">
         <v>17</v>
       </c>
@@ -2560,7 +2554,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="B105" s="10" t="s">
         <v>20</v>
       </c>
@@ -2568,7 +2562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="B106" s="10" t="s">
         <v>22</v>
       </c>
@@ -2576,7 +2570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="B107" s="10" t="s">
         <v>30</v>
       </c>
@@ -2584,7 +2578,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="B108" s="10" t="s">
         <v>24</v>
       </c>
@@ -2592,16 +2586,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="C109" s="16"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C110" s="16"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="B111" s="10" t="s">
         <v>11</v>
       </c>
@@ -2609,7 +2603,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="B112" s="10" t="s">
         <v>13</v>
       </c>
@@ -2617,7 +2611,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="B113" s="10" t="s">
         <v>2</v>
       </c>
@@ -2625,7 +2619,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="B114" s="10" t="s">
         <v>14</v>
       </c>
@@ -2634,7 +2628,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="B115" s="10" t="s">
         <v>15</v>
       </c>
@@ -2642,7 +2636,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="B116" s="10" t="s">
         <v>17</v>
       </c>
@@ -2650,7 +2644,7 @@
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="B117" s="10" t="s">
         <v>20</v>
       </c>
@@ -2658,7 +2652,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="B118" s="10" t="s">
         <v>22</v>
       </c>
@@ -2666,7 +2660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="B119" s="10" t="s">
         <v>30</v>
       </c>
@@ -2674,7 +2668,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="B120" s="10" t="s">
         <v>24</v>
       </c>
@@ -2682,16 +2676,16 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="C121" s="16"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="10" t="s">
         <v>51</v>
       </c>
       <c r="C122" s="12"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="B123" s="10" t="s">
         <v>11</v>
       </c>
@@ -2699,7 +2693,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="B124" s="10" t="s">
         <v>13</v>
       </c>
@@ -2707,7 +2701,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="B125" s="10" t="s">
         <v>2</v>
       </c>
@@ -2715,13 +2709,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="B126" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="19"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="B127" s="10" t="s">
         <v>15</v>
       </c>
@@ -2729,32 +2723,32 @@
         <v>53</v>
       </c>
     </row>
-    <row r="128">
-      <c r="B128" s="20" t="s">
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="B128" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C128" s="19" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="129">
-      <c r="B129" s="21" t="s">
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="B129" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C129" s="22" t="s">
+      <c r="C129" s="21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="C130" s="16"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="10" t="s">
         <v>58</v>
       </c>
       <c r="C131" s="12"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="B132" s="10" t="s">
         <v>11</v>
       </c>
@@ -2762,7 +2756,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="B133" s="10" t="s">
         <v>13</v>
       </c>
@@ -2770,7 +2764,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="B134" s="10" t="s">
         <v>2</v>
       </c>
@@ -2778,13 +2772,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="B135" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C135" s="19"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="B136" s="10" t="s">
         <v>15</v>
       </c>
@@ -2792,32 +2786,32 @@
         <v>59</v>
       </c>
     </row>
-    <row r="137">
-      <c r="B137" s="20" t="s">
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="B137" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C137" s="19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="138">
-      <c r="B138" s="21" t="s">
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="B138" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C138" s="22" t="s">
+      <c r="C138" s="21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="C139" s="16"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="10" t="s">
         <v>62</v>
       </c>
       <c r="C140" s="12"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="B141" s="10" t="s">
         <v>11</v>
       </c>
@@ -2825,7 +2819,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="B142" s="10" t="s">
         <v>13</v>
       </c>
@@ -2833,7 +2827,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="B143" s="10" t="s">
         <v>2</v>
       </c>
@@ -2841,13 +2835,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="B144" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C144" s="19"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="B145" s="10" t="s">
         <v>15</v>
       </c>
@@ -2855,32 +2849,32 @@
         <v>63</v>
       </c>
     </row>
-    <row r="146">
-      <c r="B146" s="20" t="s">
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="B146" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C146" s="19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="147">
-      <c r="B147" s="21" t="s">
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="B147" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C147" s="22" t="s">
+      <c r="C147" s="21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="C148" s="16"/>
     </row>
-    <row r="149">
-      <c r="A149" s="20" t="s">
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="10" t="s">
         <v>64</v>
       </c>
       <c r="C149" s="12"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="B150" s="10" t="s">
         <v>11</v>
       </c>
@@ -2888,7 +2882,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="B151" s="10" t="s">
         <v>13</v>
       </c>
@@ -2896,7 +2890,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="B152" s="10" t="s">
         <v>2</v>
       </c>
@@ -2904,13 +2898,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="B153" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C153" s="19"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="B154" s="10" t="s">
         <v>15</v>
       </c>
@@ -2918,32 +2912,32 @@
         <v>65</v>
       </c>
     </row>
-    <row r="155">
-      <c r="B155" s="20" t="s">
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="B155" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C155" s="19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="156">
-      <c r="B156" s="21" t="s">
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="B156" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C156" s="22" t="s">
+      <c r="C156" s="21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="C157" s="16"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="10" t="s">
         <v>66</v>
       </c>
       <c r="C158" s="12"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="B159" s="10" t="s">
         <v>11</v>
       </c>
@@ -2951,7 +2945,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="B160" s="10" t="s">
         <v>13</v>
       </c>
@@ -2959,7 +2953,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="B161" s="10" t="s">
         <v>2</v>
       </c>
@@ -2967,13 +2961,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="B162" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C162" s="19"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="B163" s="10" t="s">
         <v>15</v>
       </c>
@@ -2981,32 +2975,32 @@
         <v>67</v>
       </c>
     </row>
-    <row r="164">
-      <c r="B164" s="20" t="s">
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="B164" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C164" s="19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="165">
-      <c r="B165" s="21" t="s">
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="B165" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C165" s="22" t="s">
+      <c r="C165" s="21" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="C166" s="16"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="10" t="s">
         <v>69</v>
       </c>
       <c r="C167" s="12"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="B168" s="10" t="s">
         <v>11</v>
       </c>
@@ -3014,7 +3008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="B169" s="10" t="s">
         <v>13</v>
       </c>
@@ -3022,7 +3016,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="B170" s="10" t="s">
         <v>2</v>
       </c>
@@ -3030,13 +3024,13 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="B171" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C171" s="19"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="B172" s="10" t="s">
         <v>15</v>
       </c>
@@ -3044,19 +3038,19 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173">
-      <c r="B173" s="20" t="s">
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="B173" s="10" t="s">
         <v>54</v>
       </c>
       <c r="C173" s="19" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="174">
-      <c r="B174" s="21" t="s">
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="B174" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C174" s="22" t="s">
+      <c r="C174" s="21" t="s">
         <v>72</v>
       </c>
     </row>
